--- a/outputs/daily/hr_rankings_2026-10-28.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.5</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>28.5</v>
       </c>
       <c r="R2" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>18.6</v>
       </c>
       <c r="R3" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,26 +1918,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>28.5</v>
       </c>
       <c r="R6" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1989,22 +1989,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2019,67 +2019,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2198,26 +2198,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>28.5</v>
       </c>
       <c r="R7" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2269,22 +2269,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2299,67 +2299,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>28.5</v>
       </c>
       <c r="R9" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
         <v>52.4</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
         <v>52.4</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
         <v>94.90000000000001</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>28.5</v>
       </c>
       <c r="R14" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>28.5</v>
       </c>
       <c r="R16" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>18.6</v>
       </c>
       <c r="R17" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>18.6</v>
       </c>
       <c r="R18" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
         <v>64.3</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>17.3</v>
       </c>
       <c r="R19" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.5</v>
+        <v>54.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>28.5</v>
       </c>
       <c r="R2" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>18.6</v>
       </c>
       <c r="R3" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7284,26 +7284,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
         <v>28.5</v>
       </c>
       <c r="R6" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7355,22 +7355,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -7385,67 +7385,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7564,26 +7564,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>28.5</v>
       </c>
       <c r="R7" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7635,22 +7635,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -7665,67 +7665,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.6</v>
+        <v>45.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>28.5</v>
       </c>
       <c r="R9" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
         <v>52.4</v>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
         <v>52.4</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
         <v>94.90000000000001</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>28.5</v>
       </c>
       <c r="R14" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
         <v>44.8</v>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>28.5</v>
       </c>
       <c r="R16" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>18.6</v>
       </c>
       <c r="R17" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
         <v>76.2</v>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>18.6</v>
       </c>
       <c r="R18" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
         <v>64.3</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>17.3</v>
       </c>
       <c r="R19" t="n">
-        <v>40.1</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
         <v>44.8</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
